--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/99.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/99.xlsx
@@ -426,13 +426,13 @@
         <v>9.175740458584976</v>
       </c>
       <c r="E2">
-        <v>-7.16670617108461</v>
+        <v>-8.09870234965523</v>
       </c>
       <c r="F2">
-        <v>-6.542335307509729</v>
+        <v>-6.873927051197059</v>
       </c>
       <c r="G2">
-        <v>-0.9619677428855611</v>
+        <v>-4.063913199986896</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>9.519676409065847</v>
       </c>
       <c r="E3">
-        <v>-7.103153566860964</v>
+        <v>-9.421347338497535</v>
       </c>
       <c r="F3">
-        <v>-6.450237833850181</v>
+        <v>-6.778673083549144</v>
       </c>
       <c r="G3">
-        <v>-1.410773227786409</v>
+        <v>-5.240716749838624</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>9.82329513180205</v>
       </c>
       <c r="E4">
-        <v>-8.000923538881613</v>
+        <v>-10.82998352027149</v>
       </c>
       <c r="F4">
-        <v>-6.638125228867255</v>
+        <v>-7.021051728873474</v>
       </c>
       <c r="G4">
-        <v>-1.209053569976426</v>
+        <v>-3.966864509923199</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>10.0495190887475</v>
       </c>
       <c r="E5">
-        <v>-6.742270416241698</v>
+        <v>-10.99981035250715</v>
       </c>
       <c r="F5">
-        <v>-6.515205032516941</v>
+        <v>-6.796355414129302</v>
       </c>
       <c r="G5">
-        <v>-1.28850835003838</v>
+        <v>-4.782520408834645</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>10.19983513676614</v>
       </c>
       <c r="E6">
-        <v>-8.83818404121177</v>
+        <v>-13.15510132866579</v>
       </c>
       <c r="F6">
-        <v>-6.411393615414406</v>
+        <v>-6.21150980366999</v>
       </c>
       <c r="G6">
-        <v>-0.8669632538533988</v>
+        <v>-4.962081977453698</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>10.28671424540471</v>
       </c>
       <c r="E7">
-        <v>-10.35048604996932</v>
+        <v>-11.66624322984595</v>
       </c>
       <c r="F7">
-        <v>-6.334477631145965</v>
+        <v>-6.902797726103128</v>
       </c>
       <c r="G7">
-        <v>-0.6756877242671285</v>
+        <v>-5.150305970989685</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>10.33196892087696</v>
       </c>
       <c r="E8">
-        <v>-9.777869568647414</v>
+        <v>-12.97830970340634</v>
       </c>
       <c r="F8">
-        <v>-6.569837105282673</v>
+        <v>-6.647723936147195</v>
       </c>
       <c r="G8">
-        <v>-1.170692808724958</v>
+        <v>-4.727044795929113</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>10.34174467311376</v>
       </c>
       <c r="E9">
-        <v>-10.0581775812482</v>
+        <v>-13.22478095822181</v>
       </c>
       <c r="F9">
-        <v>-6.389659739867155</v>
+        <v>-6.726773794845248</v>
       </c>
       <c r="G9">
-        <v>-1.198530692435287</v>
+        <v>-5.155949672071929</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>10.33405728242994</v>
       </c>
       <c r="E10">
-        <v>-10.97074207785191</v>
+        <v>-13.71097151310733</v>
       </c>
       <c r="F10">
-        <v>-6.139119604706743</v>
+        <v>-6.660840719786824</v>
       </c>
       <c r="G10">
-        <v>-1.015159625585719</v>
+        <v>-5.339350269915532</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>10.33178872570458</v>
       </c>
       <c r="E11">
-        <v>-11.92446587471133</v>
+        <v>-12.95105734682818</v>
       </c>
       <c r="F11">
-        <v>-6.143279665803602</v>
+        <v>-6.419463156468777</v>
       </c>
       <c r="G11">
-        <v>-1.687642702972354</v>
+        <v>-3.91681275625543</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>10.34190856430839</v>
       </c>
       <c r="E12">
-        <v>-12.38414674275594</v>
+        <v>-13.82165647480281</v>
       </c>
       <c r="F12">
-        <v>-6.210116489698481</v>
+        <v>-6.552066139390415</v>
       </c>
       <c r="G12">
-        <v>-0.8136302786261844</v>
+        <v>-5.009741720604633</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>10.35910245985773</v>
       </c>
       <c r="E13">
-        <v>-13.18110835489184</v>
+        <v>-15.70272117895296</v>
       </c>
       <c r="F13">
-        <v>-5.968229894611413</v>
+        <v>-6.127191942473833</v>
       </c>
       <c r="G13">
-        <v>-1.063469050605424</v>
+        <v>-3.128971772503397</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>10.3931566619156</v>
       </c>
       <c r="E14">
-        <v>-14.07734317422389</v>
+        <v>-14.93368666602237</v>
       </c>
       <c r="F14">
-        <v>-5.605306396464298</v>
+        <v>-5.665536990321849</v>
       </c>
       <c r="G14">
-        <v>-1.448264465324625</v>
+        <v>-3.839316865464465</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>10.43464973327213</v>
       </c>
       <c r="E15">
-        <v>-14.61983171797276</v>
+        <v>-16.70414792100919</v>
       </c>
       <c r="F15">
-        <v>-5.31971845067514</v>
+        <v>-6.04025892538704</v>
       </c>
       <c r="G15">
-        <v>-0.8354766517689673</v>
+        <v>-3.115459702121604</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>10.46174960470871</v>
       </c>
       <c r="E16">
-        <v>-16.28729736012912</v>
+        <v>-18.55393898366238</v>
       </c>
       <c r="F16">
-        <v>-5.076373100591743</v>
+        <v>-5.032538382737801</v>
       </c>
       <c r="G16">
-        <v>-0.1296432384521362</v>
+        <v>-4.063903356322218</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>10.4752206255558</v>
       </c>
       <c r="E17">
-        <v>-16.79380717788705</v>
+        <v>-18.36090825061142</v>
       </c>
       <c r="F17">
-        <v>-4.805467967017207</v>
+        <v>-4.891171686878246</v>
       </c>
       <c r="G17">
-        <v>-0.6161171468554097</v>
+        <v>-4.010298039705569</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>10.46849881540218</v>
       </c>
       <c r="E18">
-        <v>-16.74667029194121</v>
+        <v>-19.18653057474186</v>
       </c>
       <c r="F18">
-        <v>-4.640733026724678</v>
+        <v>-5.130158996055515</v>
       </c>
       <c r="G18">
-        <v>0.07778246364972098</v>
+        <v>-3.636671903174718</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>10.42396485423354</v>
       </c>
       <c r="E19">
-        <v>-18.47900179578345</v>
+        <v>-20.12930904992475</v>
       </c>
       <c r="F19">
-        <v>-4.368886039413158</v>
+        <v>-4.687286446394607</v>
       </c>
       <c r="G19">
-        <v>0.3205108285096439</v>
+        <v>-3.009879836003351</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>10.34389409697169</v>
       </c>
       <c r="E20">
-        <v>-19.85835686462381</v>
+        <v>-21.20169697968116</v>
       </c>
       <c r="F20">
-        <v>-3.783075380929584</v>
+        <v>-4.101831157526834</v>
       </c>
       <c r="G20">
-        <v>-0.3238784298850256</v>
+        <v>-2.538765325719838</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>10.23115093751133</v>
       </c>
       <c r="E21">
-        <v>-19.66473742995185</v>
+        <v>-22.56108600662171</v>
       </c>
       <c r="F21">
-        <v>-3.188400362868653</v>
+        <v>-4.352964817931351</v>
       </c>
       <c r="G21">
-        <v>0.6352160694975459</v>
+        <v>-3.221945185390263</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>10.07866137001894</v>
       </c>
       <c r="E22">
-        <v>-20.76456791219475</v>
+        <v>-21.6414978468321</v>
       </c>
       <c r="F22">
-        <v>-2.87147527823159</v>
+        <v>-3.641894239368256</v>
       </c>
       <c r="G22">
-        <v>0.03252457468030002</v>
+        <v>-3.468775077199492</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>9.887729256517892</v>
       </c>
       <c r="E23">
-        <v>-20.81839335424992</v>
+        <v>-25.23390910627295</v>
       </c>
       <c r="F23">
-        <v>-2.939649915481989</v>
+        <v>-2.680584637195666</v>
       </c>
       <c r="G23">
-        <v>-0.3348869282169626</v>
+        <v>-2.810145317236832</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>9.67367597342426</v>
       </c>
       <c r="E24">
-        <v>-21.58512740238462</v>
+        <v>-23.8070322311961</v>
       </c>
       <c r="F24">
-        <v>-2.414398712714878</v>
+        <v>-3.640435484371926</v>
       </c>
       <c r="G24">
-        <v>-0.7599265253627527</v>
+        <v>-3.584477511828631</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>9.441939469636836</v>
       </c>
       <c r="E25">
-        <v>-21.59518514315566</v>
+        <v>-22.12246707118677</v>
       </c>
       <c r="F25">
-        <v>-2.379397704844391</v>
+        <v>-3.286277770081234</v>
       </c>
       <c r="G25">
-        <v>-0.5574259368216221</v>
+        <v>-3.451506008132134</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>9.194078189647575</v>
       </c>
       <c r="E26">
-        <v>-21.83677017451685</v>
+        <v>-23.51386335241353</v>
       </c>
       <c r="F26">
-        <v>-1.709783601321799</v>
+        <v>-2.803096862600102</v>
       </c>
       <c r="G26">
-        <v>-0.6598853612368428</v>
+        <v>-4.101181314459069</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>8.954581628482039</v>
       </c>
       <c r="E27">
-        <v>-21.92565959081342</v>
+        <v>-23.66384188307356</v>
       </c>
       <c r="F27">
-        <v>-2.085375322159929</v>
+        <v>-2.139179441706562</v>
       </c>
       <c r="G27">
-        <v>0.2524090750433687</v>
+        <v>-3.992097103715329</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>8.735102813759497</v>
       </c>
       <c r="E28">
-        <v>-21.92963106251814</v>
+        <v>-24.91661251797751</v>
       </c>
       <c r="F28">
-        <v>-1.964692131980874</v>
+        <v>-1.869843235992928</v>
       </c>
       <c r="G28">
-        <v>-0.9746529454343744</v>
+        <v>-3.119836851681903</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>8.537084254008027</v>
       </c>
       <c r="E29">
-        <v>-21.48579985350038</v>
+        <v>-23.65007079361624</v>
       </c>
       <c r="F29">
-        <v>-1.714159866310789</v>
+        <v>-2.13473442222314</v>
       </c>
       <c r="G29">
-        <v>-0.9106494376958457</v>
+        <v>-2.838577102049421</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>8.386319397876813</v>
       </c>
       <c r="E30">
-        <v>-20.78446602698446</v>
+        <v>-22.17995152024014</v>
       </c>
       <c r="F30">
-        <v>-2.097047847232777</v>
+        <v>-2.354226932942925</v>
       </c>
       <c r="G30">
-        <v>-1.61752627946858</v>
+        <v>-4.093719816632892</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>8.300636810826942</v>
       </c>
       <c r="E31">
-        <v>-21.28904218634111</v>
+        <v>-22.89349411268074</v>
       </c>
       <c r="F31">
-        <v>-1.795099645238329</v>
+        <v>-3.000651719391547</v>
       </c>
       <c r="G31">
-        <v>-0.6566894514379437</v>
+        <v>-3.489656771203798</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>8.281154464872461</v>
       </c>
       <c r="E32">
-        <v>-20.44249831229523</v>
+        <v>-23.47613210698162</v>
       </c>
       <c r="F32">
-        <v>-2.318603821152935</v>
+        <v>-2.731955841680277</v>
       </c>
       <c r="G32">
-        <v>-1.472027071858123</v>
+        <v>-4.615867165830448</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>8.344762270504786</v>
       </c>
       <c r="E33">
-        <v>-19.29323047931059</v>
+        <v>-22.34207541818875</v>
       </c>
       <c r="F33">
-        <v>-1.977735605105355</v>
+        <v>-2.898292844529821</v>
       </c>
       <c r="G33">
-        <v>-1.183647071441646</v>
+        <v>-3.629653370259066</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>8.503682458897876</v>
       </c>
       <c r="E34">
-        <v>-18.79781089439745</v>
+        <v>-21.86276361532088</v>
       </c>
       <c r="F34">
-        <v>-2.320130502276295</v>
+        <v>-2.92772556671869</v>
       </c>
       <c r="G34">
-        <v>-1.152468904183802</v>
+        <v>-2.972703595734842</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>8.749792545429035</v>
       </c>
       <c r="E35">
-        <v>-19.1336515837543</v>
+        <v>-19.86557978066604</v>
       </c>
       <c r="F35">
-        <v>-2.440996761651368</v>
+        <v>-2.650808142534635</v>
       </c>
       <c r="G35">
-        <v>-1.166555188338499</v>
+        <v>-3.12145121268915</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>9.074848937947612</v>
       </c>
       <c r="E36">
-        <v>-18.33741452745963</v>
+        <v>-20.77847485587231</v>
       </c>
       <c r="F36">
-        <v>-2.660986292812832</v>
+        <v>-2.433306198683777</v>
       </c>
       <c r="G36">
-        <v>-0.9913970190522208</v>
+        <v>-3.352947956151093</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>9.478347535670547</v>
       </c>
       <c r="E37">
-        <v>-18.08554986010101</v>
+        <v>-18.49132377355832</v>
       </c>
       <c r="F37">
-        <v>-2.61871056241096</v>
+        <v>-3.269979641431153</v>
       </c>
       <c r="G37">
-        <v>-1.096576576140221</v>
+        <v>-2.593617506529076</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>9.93976908496796</v>
       </c>
       <c r="E38">
-        <v>-16.45584716269461</v>
+        <v>-18.8144892641677</v>
       </c>
       <c r="F38">
-        <v>-2.484032933329011</v>
+        <v>-3.444446241971771</v>
       </c>
       <c r="G38">
-        <v>-1.407429663017335</v>
+        <v>-2.904710122580029</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>10.42871148514413</v>
       </c>
       <c r="E39">
-        <v>-18.67369900726922</v>
+        <v>-19.19325083016924</v>
       </c>
       <c r="F39">
-        <v>-2.202961246619916</v>
+        <v>-3.606345680644518</v>
       </c>
       <c r="G39">
-        <v>-1.217994898725913</v>
+        <v>-3.821906703870051</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>10.93772698055576</v>
       </c>
       <c r="E40">
-        <v>-16.12459834598154</v>
+        <v>-18.90147672138104</v>
       </c>
       <c r="F40">
-        <v>-2.741356154967246</v>
+        <v>-2.995686485179167</v>
       </c>
       <c r="G40">
-        <v>-0.4600688119313379</v>
+        <v>-2.503351101428752</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>11.4460633825112</v>
       </c>
       <c r="E41">
-        <v>-16.21810680576593</v>
+        <v>-17.59732602038606</v>
       </c>
       <c r="F41">
-        <v>-2.656827060083376</v>
+        <v>-3.249492458825116</v>
       </c>
       <c r="G41">
-        <v>-0.3015431547298854</v>
+        <v>-3.678520602943876</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>11.92123197930031</v>
       </c>
       <c r="E42">
-        <v>-14.60788560354053</v>
+        <v>-16.18896154705256</v>
       </c>
       <c r="F42">
-        <v>-2.80059602141105</v>
+        <v>-3.585626555165697</v>
       </c>
       <c r="G42">
-        <v>-0.1767090805008112</v>
+        <v>-4.431390327315348</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>12.35890637472316</v>
       </c>
       <c r="E43">
-        <v>-13.77692873702905</v>
+        <v>-13.46024349272464</v>
       </c>
       <c r="F43">
-        <v>-3.029316544998021</v>
+        <v>-3.109176132832311</v>
       </c>
       <c r="G43">
-        <v>0.009431337344928108</v>
+        <v>-3.374387457820505</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>12.74916482537126</v>
       </c>
       <c r="E44">
-        <v>-14.03838018386189</v>
+        <v>-14.79521951628983</v>
       </c>
       <c r="F44">
-        <v>-3.01489715361749</v>
+        <v>-3.453342079510435</v>
       </c>
       <c r="G44">
-        <v>-0.2833126877456105</v>
+        <v>-2.809991099823538</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>13.06960089657058</v>
       </c>
       <c r="E45">
-        <v>-12.70703599645086</v>
+        <v>-13.81723215569731</v>
       </c>
       <c r="F45">
-        <v>-2.760660428922086</v>
+        <v>-3.051320468318585</v>
       </c>
       <c r="G45">
-        <v>-0.1557716057299944</v>
+        <v>-2.840791926602046</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>13.3182739490159</v>
       </c>
       <c r="E46">
-        <v>-11.7670515897307</v>
+        <v>-12.77554275123889</v>
       </c>
       <c r="F46">
-        <v>-2.763741127293097</v>
+        <v>-3.469170523843128</v>
       </c>
       <c r="G46">
-        <v>-0.1988442011408252</v>
+        <v>-3.179807738123874</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>13.49682741270724</v>
       </c>
       <c r="E47">
-        <v>-10.88111904876611</v>
+        <v>-13.52199376429324</v>
       </c>
       <c r="F47">
-        <v>-2.8927237304808</v>
+        <v>-3.148148334031819</v>
       </c>
       <c r="G47">
-        <v>-0.3892075511335699</v>
+        <v>-2.376604075030521</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>13.59605278723555</v>
       </c>
       <c r="E48">
-        <v>-10.57258505767551</v>
+        <v>-11.17646159507236</v>
       </c>
       <c r="F48">
-        <v>-2.802695932777147</v>
+        <v>-3.038688693793295</v>
       </c>
       <c r="G48">
-        <v>0.2862876876446355</v>
+        <v>-2.739572803936295</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>13.61262281244663</v>
       </c>
       <c r="E49">
-        <v>-9.813087511005067</v>
+        <v>-9.67994584670555</v>
       </c>
       <c r="F49">
-        <v>-2.97701922575708</v>
+        <v>-3.150114878246065</v>
       </c>
       <c r="G49">
-        <v>0.2633716362734735</v>
+        <v>-1.79816736998069</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>13.55936965719265</v>
       </c>
       <c r="E50">
-        <v>-8.44235918514932</v>
+        <v>-8.209736003849301</v>
       </c>
       <c r="F50">
-        <v>-3.415084759379543</v>
+        <v>-2.90505397927147</v>
       </c>
       <c r="G50">
-        <v>-0.2840050254946534</v>
+        <v>-2.511229314392978</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>13.43595329539783</v>
       </c>
       <c r="E51">
-        <v>-7.305082751336993</v>
+        <v>-7.228470028075226</v>
       </c>
       <c r="F51">
-        <v>-2.883528023942322</v>
+        <v>-2.796199875604393</v>
       </c>
       <c r="G51">
-        <v>0.9210924978641668</v>
+        <v>-1.651191612668483</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>13.23522605908367</v>
       </c>
       <c r="E52">
-        <v>-6.946287227235263</v>
+        <v>-8.857683650288799</v>
       </c>
       <c r="F52">
-        <v>-3.13595476586261</v>
+        <v>-3.515335439201145</v>
       </c>
       <c r="G52">
-        <v>0.3876380591727638</v>
+        <v>-3.727666739461239</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>12.97525533494593</v>
       </c>
       <c r="E53">
-        <v>-5.805311030158671</v>
+        <v>-6.756539637839867</v>
       </c>
       <c r="F53">
-        <v>-2.645083295413888</v>
+        <v>-2.835080128022191</v>
       </c>
       <c r="G53">
-        <v>0.6753749401635898</v>
+        <v>-3.360261799007096</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>12.66143202616612</v>
       </c>
       <c r="E54">
-        <v>-6.652031514690851</v>
+        <v>-8.067274740041999</v>
       </c>
       <c r="F54">
-        <v>-2.664759506332584</v>
+        <v>-3.479173888599335</v>
       </c>
       <c r="G54">
-        <v>-0.2136392291523614</v>
+        <v>-3.597881301898963</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>12.28750531364873</v>
       </c>
       <c r="E55">
-        <v>-4.678327817765779</v>
+        <v>-9.623896923912614</v>
       </c>
       <c r="F55">
-        <v>-2.296168318415513</v>
+        <v>-2.998793691307068</v>
       </c>
       <c r="G55">
-        <v>-0.04351445373827183</v>
+        <v>-2.286806884613197</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>11.87210614541478</v>
       </c>
       <c r="E56">
-        <v>-4.60537410150221</v>
+        <v>-3.579620397076782</v>
       </c>
       <c r="F56">
-        <v>-2.658984957167669</v>
+        <v>-3.074648951116224</v>
       </c>
       <c r="G56">
-        <v>-0.0446792873918747</v>
+        <v>-3.574988219078717</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>11.42811868318408</v>
       </c>
       <c r="E57">
-        <v>-4.021495305323232</v>
+        <v>-7.445886593657487</v>
       </c>
       <c r="F57">
-        <v>-2.213235487516838</v>
+        <v>-2.844979118485645</v>
       </c>
       <c r="G57">
-        <v>0.9951496684608341</v>
+        <v>-2.486091876026072</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>10.95627192461809</v>
       </c>
       <c r="E58">
-        <v>-2.986082365839443</v>
+        <v>-4.866757621224942</v>
       </c>
       <c r="F58">
-        <v>-2.797302432617519</v>
+        <v>-3.294278142457471</v>
       </c>
       <c r="G58">
-        <v>0.444606627887843</v>
+        <v>-3.344492248192404</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>10.4731678763546</v>
       </c>
       <c r="E59">
-        <v>-2.77253764553374</v>
+        <v>-6.037218712565477</v>
       </c>
       <c r="F59">
-        <v>-2.697318487099619</v>
+        <v>-3.249234836562845</v>
       </c>
       <c r="G59">
-        <v>-0.2239488272921367</v>
+        <v>-1.76791450720261</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>10.00110514059125</v>
       </c>
       <c r="E60">
-        <v>-2.173533746169143</v>
+        <v>-3.440904181273823</v>
       </c>
       <c r="F60">
-        <v>-2.474013001224748</v>
+        <v>-2.515166293795827</v>
       </c>
       <c r="G60">
-        <v>0.9807090123777179</v>
+        <v>-4.150649010689257</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>9.548744040284745</v>
       </c>
       <c r="E61">
-        <v>-1.755723148799453</v>
+        <v>-3.379008998536985</v>
       </c>
       <c r="F61">
-        <v>-2.413194266511208</v>
+        <v>-3.088807406764873</v>
       </c>
       <c r="G61">
-        <v>-0.8007580464484828</v>
+        <v>-3.776330536409364</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>9.125494581681128</v>
       </c>
       <c r="E62">
-        <v>-1.999291651776011</v>
+        <v>-3.920976767774973</v>
       </c>
       <c r="F62">
-        <v>-2.572487661334747</v>
+        <v>-2.887987125671592</v>
       </c>
       <c r="G62">
-        <v>-0.2065780403564364</v>
+        <v>-3.360199455797466</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>8.75783720813404</v>
       </c>
       <c r="E63">
-        <v>-0.5811637884819773</v>
+        <v>-3.758246054309339</v>
       </c>
       <c r="F63">
-        <v>-2.788282339968435</v>
+        <v>-3.56044087265098</v>
       </c>
       <c r="G63">
-        <v>0.0695433163139553</v>
+        <v>-3.745818457128087</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>8.453882539309499</v>
       </c>
       <c r="E64">
-        <v>-1.07520671729679</v>
+        <v>-0.9340451255296899</v>
       </c>
       <c r="F64">
-        <v>-2.757902793838166</v>
+        <v>-3.460708750823531</v>
       </c>
       <c r="G64">
-        <v>-0.4552815096761081</v>
+        <v>-4.709352449280588</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>8.210193801915739</v>
       </c>
       <c r="E65">
-        <v>-0.1006519400020833</v>
+        <v>-1.840740719819457</v>
       </c>
       <c r="F65">
-        <v>-2.899333273987737</v>
+        <v>-3.364874097626254</v>
       </c>
       <c r="G65">
-        <v>-0.845346566219777</v>
+        <v>-2.701074231379331</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>8.044638317176471</v>
       </c>
       <c r="E66">
-        <v>-0.624193348502861</v>
+        <v>-2.22361414021997</v>
       </c>
       <c r="F66">
-        <v>-2.830042825845767</v>
+        <v>-3.2183889195848</v>
       </c>
       <c r="G66">
-        <v>0.1099023414951253</v>
+        <v>-2.227964738387675</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>7.958018885062274</v>
       </c>
       <c r="E67">
-        <v>-0.5185531068519269</v>
+        <v>0.07858506122150942</v>
       </c>
       <c r="F67">
-        <v>-3.040078694295193</v>
+        <v>-3.563036147723951</v>
       </c>
       <c r="G67">
-        <v>-1.181110687176195</v>
+        <v>-3.50128213918891</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>7.934289377317372</v>
       </c>
       <c r="E68">
-        <v>-1.018985712491563</v>
+        <v>-1.9444971162832</v>
       </c>
       <c r="F68">
-        <v>-3.121231363645252</v>
+        <v>-3.925840360965065</v>
       </c>
       <c r="G68">
-        <v>-0.799232278423341</v>
+        <v>-2.959519647508993</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>7.977602623713068</v>
       </c>
       <c r="E69">
-        <v>-0.9349870481232854</v>
+        <v>-1.375879277510071</v>
       </c>
       <c r="F69">
-        <v>-3.131369752288115</v>
+        <v>-4.14509347350544</v>
       </c>
       <c r="G69">
-        <v>-0.09227668733317974</v>
+        <v>-2.799720876342477</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>8.083275618384615</v>
       </c>
       <c r="E70">
-        <v>0.5769390972916246</v>
+        <v>-1.184211615135423</v>
       </c>
       <c r="F70">
-        <v>-3.512673066368547</v>
+        <v>-3.867899374608851</v>
       </c>
       <c r="G70">
-        <v>-0.584525545681076</v>
+        <v>-3.819888752610992</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>8.231543517384047</v>
       </c>
       <c r="E71">
-        <v>0.2207021610042282</v>
+        <v>-1.994174476147344</v>
       </c>
       <c r="F71">
-        <v>-3.666769284106922</v>
+        <v>-4.224190963329154</v>
       </c>
       <c r="G71">
-        <v>-0.864249683623738</v>
+        <v>-3.429741665528337</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>8.415386574842172</v>
       </c>
       <c r="E72">
-        <v>0.4156982517745139</v>
+        <v>-0.04381506273181267</v>
       </c>
       <c r="F72">
-        <v>-3.720000173410818</v>
+        <v>-3.768570667706565</v>
       </c>
       <c r="G72">
-        <v>-0.4738335363732085</v>
+        <v>-2.666591874011126</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>8.632253944471246</v>
       </c>
       <c r="E73">
-        <v>0.03968094102161338</v>
+        <v>-3.063664182538852</v>
       </c>
       <c r="F73">
-        <v>-3.685461394551093</v>
+        <v>-4.270042755808912</v>
       </c>
       <c r="G73">
-        <v>-0.08499893791433137</v>
+        <v>-4.205917906636544</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>8.866817720122411</v>
       </c>
       <c r="E74">
-        <v>-0.06191990181447876</v>
+        <v>-1.344963385459706</v>
       </c>
       <c r="F74">
-        <v>-3.682271351682912</v>
+        <v>-4.223056099987319</v>
       </c>
       <c r="G74">
-        <v>0.3695125912783912</v>
+        <v>-3.112335979197012</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>9.105822003873726</v>
       </c>
       <c r="E75">
-        <v>-0.928053954417542</v>
+        <v>-0.6062922907505401</v>
       </c>
       <c r="F75">
-        <v>-4.110022882773118</v>
+        <v>-3.792253691752602</v>
       </c>
       <c r="G75">
-        <v>-0.2264917740007064</v>
+        <v>-3.104618546089198</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>9.353812610364189</v>
       </c>
       <c r="E76">
-        <v>-1.111122044651624</v>
+        <v>-2.101970271425929</v>
       </c>
       <c r="F76">
-        <v>-3.894558722733147</v>
+        <v>-5.308925651784065</v>
       </c>
       <c r="G76">
-        <v>-0.1622290497589816</v>
+        <v>-2.592482203869507</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>9.603659990955249</v>
       </c>
       <c r="E77">
-        <v>-0.7094464001712631</v>
+        <v>-4.029628444641008</v>
       </c>
       <c r="F77">
-        <v>-4.429546555952763</v>
+        <v>-4.743807611022422</v>
       </c>
       <c r="G77">
-        <v>0.5218990829421227</v>
+        <v>-1.986171521672194</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>9.841162803006792</v>
       </c>
       <c r="E78">
-        <v>-1.042438679377288</v>
+        <v>-4.185552861673114</v>
       </c>
       <c r="F78">
-        <v>-4.084338523081916</v>
+        <v>-4.567917875283795</v>
       </c>
       <c r="G78">
-        <v>1.278197683843214</v>
+        <v>-2.125570938403643</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>10.07402998927769</v>
       </c>
       <c r="E79">
-        <v>-2.863541859191884</v>
+        <v>-4.157000833054752</v>
       </c>
       <c r="F79">
-        <v>-4.600967249553287</v>
+        <v>-4.831394209990026</v>
       </c>
       <c r="G79">
-        <v>1.004740679079091</v>
+        <v>-1.745654700143337</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>10.30006611532811</v>
       </c>
       <c r="E80">
-        <v>-3.899634069776823</v>
+        <v>-4.542772476820175</v>
       </c>
       <c r="F80">
-        <v>-4.809787903022806</v>
+        <v>-4.744831473132283</v>
       </c>
       <c r="G80">
-        <v>1.826351995120929</v>
+        <v>-1.322026028268108</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>10.50276894548126</v>
       </c>
       <c r="E81">
-        <v>-4.390529709156305</v>
+        <v>-5.261785465862044</v>
       </c>
       <c r="F81">
-        <v>-4.754050373958038</v>
+        <v>-5.991380278417451</v>
       </c>
       <c r="G81">
-        <v>2.02164373989596</v>
+        <v>0.00226514945910085</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>10.68735614223634</v>
       </c>
       <c r="E82">
-        <v>-4.842942376418605</v>
+        <v>-6.559084585683417</v>
       </c>
       <c r="F82">
-        <v>-4.954668533405036</v>
+        <v>-4.739984695458503</v>
       </c>
       <c r="G82">
-        <v>1.607228738159651</v>
+        <v>0.8159785652073553</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>10.85320198312804</v>
       </c>
       <c r="E83">
-        <v>-6.310942323959112</v>
+        <v>-8.304064117429075</v>
       </c>
       <c r="F83">
-        <v>-5.004516370235899</v>
+        <v>-5.52300892336357</v>
       </c>
       <c r="G83">
-        <v>2.888591694224645</v>
+        <v>1.684599942531358</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>10.98678686578831</v>
       </c>
       <c r="E84">
-        <v>-7.254477054301277</v>
+        <v>-7.677558795415895</v>
       </c>
       <c r="F84">
-        <v>-5.225822177200413</v>
+        <v>-5.546657155978689</v>
       </c>
       <c r="G84">
-        <v>2.814619835388523</v>
+        <v>-0.6447884608418376</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>11.08523860711474</v>
       </c>
       <c r="E85">
-        <v>-7.070553082479745</v>
+        <v>-10.58621123596459</v>
       </c>
       <c r="F85">
-        <v>-5.252705184523466</v>
+        <v>-5.768269458882238</v>
       </c>
       <c r="G85">
-        <v>2.808575825276026</v>
+        <v>1.250343394025087</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>11.15127295781226</v>
       </c>
       <c r="E86">
-        <v>-8.587297524238817</v>
+        <v>-10.28634927259868</v>
       </c>
       <c r="F86">
-        <v>-5.493726135674606</v>
+        <v>-6.201802166076582</v>
       </c>
       <c r="G86">
-        <v>3.764070824607887</v>
+        <v>2.612053622416204</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>11.17522775288087</v>
       </c>
       <c r="E87">
-        <v>-10.84193416317773</v>
+        <v>-11.3895534679773</v>
       </c>
       <c r="F87">
-        <v>-5.659898293410993</v>
+        <v>-5.7778453860586</v>
       </c>
       <c r="G87">
-        <v>3.281334227560821</v>
+        <v>0.6187541809338118</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>11.14600545673822</v>
       </c>
       <c r="E88">
-        <v>-11.9717386148774</v>
+        <v>-13.49504028699958</v>
       </c>
       <c r="F88">
-        <v>-6.028564034394316</v>
+        <v>-6.007543383180876</v>
       </c>
       <c r="G88">
-        <v>4.127154396268242</v>
+        <v>2.165571242379443</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>11.06998375281012</v>
       </c>
       <c r="E89">
-        <v>-13.38540140279988</v>
+        <v>-15.08627359771082</v>
       </c>
       <c r="F89">
-        <v>-6.1553514639646</v>
+        <v>-6.739226227827832</v>
       </c>
       <c r="G89">
-        <v>3.063569396325153</v>
+        <v>2.273277340068215</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>10.9407458160301</v>
       </c>
       <c r="E90">
-        <v>-16.05937020637506</v>
+        <v>-15.53484159054061</v>
       </c>
       <c r="F90">
-        <v>-6.843078649116805</v>
+        <v>-6.507770020893115</v>
       </c>
       <c r="G90">
-        <v>3.134132065961012</v>
+        <v>2.971560662576764</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>10.7454030646919</v>
       </c>
       <c r="E91">
-        <v>-16.63813635539938</v>
+        <v>-17.442017475819</v>
       </c>
       <c r="F91">
-        <v>-6.880185781108911</v>
+        <v>-6.885324144108476</v>
       </c>
       <c r="G91">
-        <v>3.941040228194978</v>
+        <v>2.79579218608043</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>10.49133279510031</v>
       </c>
       <c r="E92">
-        <v>-18.87634369063847</v>
+        <v>-20.40159260658394</v>
       </c>
       <c r="F92">
-        <v>-6.967970774069484</v>
+        <v>-7.459495412215314</v>
       </c>
       <c r="G92">
-        <v>2.74538606048424</v>
+        <v>0.6898812206778949</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>10.17761880277758</v>
       </c>
       <c r="E93">
-        <v>-20.37084426807186</v>
+        <v>-23.95070712603745</v>
       </c>
       <c r="F93">
-        <v>-7.080261774090777</v>
+        <v>-7.302150337523159</v>
       </c>
       <c r="G93">
-        <v>3.74998782167475</v>
+        <v>2.138786630789695</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>9.794712601811062</v>
       </c>
       <c r="E94">
-        <v>-22.38600614453716</v>
+        <v>-22.92397527122637</v>
       </c>
       <c r="F94">
-        <v>-7.278196437336406</v>
+        <v>-7.458091329467569</v>
       </c>
       <c r="G94">
-        <v>3.825163888823188</v>
+        <v>0.7690275659132609</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>9.351775522716286</v>
       </c>
       <c r="E95">
-        <v>-23.86698922705765</v>
+        <v>-25.78839357766814</v>
       </c>
       <c r="F95">
-        <v>-7.630325065673941</v>
+        <v>-7.764290298789482</v>
       </c>
       <c r="G95">
-        <v>2.181386730295966</v>
+        <v>0.846713767554674</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>8.852100968679634</v>
       </c>
       <c r="E96">
-        <v>-26.70250681238247</v>
+        <v>-27.60393579140132</v>
       </c>
       <c r="F96">
-        <v>-7.828896329268622</v>
+        <v>-7.759986515948238</v>
       </c>
       <c r="G96">
-        <v>3.051638874735012</v>
+        <v>-0.1968623433189206</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>8.301063777106091</v>
       </c>
       <c r="E97">
-        <v>-29.33384456164945</v>
+        <v>-30.14177413783192</v>
       </c>
       <c r="F97">
-        <v>-7.971605808688115</v>
+        <v>-8.543964608917628</v>
       </c>
       <c r="G97">
-        <v>1.774607131128486</v>
+        <v>0.6918926094938346</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>7.69547200550671</v>
       </c>
       <c r="E98">
-        <v>-30.67636275867441</v>
+        <v>-31.11972074215837</v>
       </c>
       <c r="F98">
-        <v>-8.064759864969933</v>
+        <v>-8.320555991301108</v>
       </c>
       <c r="G98">
-        <v>0.1202906889523273</v>
+        <v>-1.395131644612536</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>7.071662746059014</v>
       </c>
       <c r="E99">
-        <v>-33.03971673735248</v>
+        <v>-33.40542950550093</v>
       </c>
       <c r="F99">
-        <v>-8.471890017934848</v>
+        <v>-8.287695898983156</v>
       </c>
       <c r="G99">
-        <v>0.2540923417033639</v>
+        <v>-1.498742777795122</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>6.412028984742661</v>
       </c>
       <c r="E100">
-        <v>-35.50040800058841</v>
+        <v>-36.70266124369979</v>
       </c>
       <c r="F100">
-        <v>-8.561227785591969</v>
+        <v>-8.445798929848872</v>
       </c>
       <c r="G100">
-        <v>-0.6590716182901005</v>
+        <v>-4.167822924331391</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>5.770459607469793</v>
       </c>
       <c r="E101">
-        <v>-37.71332154425766</v>
+        <v>-38.70949978493899</v>
       </c>
       <c r="F101">
-        <v>-8.400877808146159</v>
+        <v>-8.146367308024129</v>
       </c>
       <c r="G101">
-        <v>-1.461248259035347</v>
+        <v>-3.586173903374864</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>5.100772813578762</v>
       </c>
       <c r="E102">
-        <v>-40.53197509237791</v>
+        <v>-41.7308659435386</v>
       </c>
       <c r="F102">
-        <v>-8.435476643642588</v>
+        <v>-8.843070268169368</v>
       </c>
       <c r="G102">
-        <v>-2.167098078459976</v>
+        <v>-3.377698210373985</v>
       </c>
     </row>
   </sheetData>
